--- a/Overture-Match-Suggestions/ET.xlsx
+++ b/Overture-Match-Suggestions/ET.xlsx
@@ -644,10 +644,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -734,10 +748,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
@@ -824,10 +852,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
@@ -914,10 +956,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
@@ -1004,10 +1060,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -1094,10 +1164,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
@@ -1184,10 +1268,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -1274,10 +1372,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
@@ -1364,10 +1476,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -1454,10 +1580,24 @@
           <t>Addis AbabaEthiopia</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ET-AA</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>አዲስ አበባ أديس أبابا</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
@@ -1544,10 +1684,24 @@
           <t>AfarEthiopia</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ET-AF</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Zone 1</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
@@ -4238,10 +4392,24 @@
           <t>AmharaEthiopia</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>ET-AM</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Special Woreda</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
@@ -4328,10 +4496,24 @@
           <t>AmharaEthiopia</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>ET-AM</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>South Wollo</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
@@ -4418,10 +4600,24 @@
           <t>AmharaEthiopia</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ET-AM</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>South Wollo</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
@@ -4508,10 +4704,24 @@
           <t>AmharaEthiopia</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>ET-AM</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>North Gonder</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
@@ -15950,10 +16160,24 @@
           <t>Benishangul-GumuzEthiopia</t>
         </is>
       </c>
-      <c r="M183" s="4" t="n"/>
-      <c r="N183" s="4" t="n"/>
-      <c r="O183" s="4" t="n"/>
-      <c r="P183" s="4" t="n"/>
+      <c r="M183" s="4" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N183" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" s="4" t="inlineStr">
+        <is>
+          <t>ET-BE</t>
+        </is>
+      </c>
+      <c r="P183" s="4" t="inlineStr">
+        <is>
+          <t>Asosa</t>
+        </is>
+      </c>
       <c r="Q183" s="4" t="n"/>
       <c r="R183" s="4" t="n"/>
       <c r="S183" s="4" t="n"/>
@@ -17664,10 +17888,24 @@
           <t>Dire DawaEthiopia</t>
         </is>
       </c>
-      <c r="M203" s="3" t="n"/>
-      <c r="N203" s="3" t="n"/>
-      <c r="O203" s="3" t="n"/>
-      <c r="P203" s="3" t="n"/>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O203" s="3" t="inlineStr">
+        <is>
+          <t>ET-DD</t>
+        </is>
+      </c>
+      <c r="P203" s="3" t="inlineStr">
+        <is>
+          <t>Dire Dawa</t>
+        </is>
+      </c>
       <c r="Q203" s="3" t="n"/>
       <c r="R203" s="3" t="n"/>
       <c r="S203" s="3" t="n"/>
@@ -17768,10 +18006,24 @@
           <t>GambelaEthiopia</t>
         </is>
       </c>
-      <c r="M204" s="3" t="n"/>
-      <c r="N204" s="3" t="n"/>
-      <c r="O204" s="3" t="n"/>
-      <c r="P204" s="3" t="n"/>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" s="3" t="inlineStr">
+        <is>
+          <t>ET-GA</t>
+        </is>
+      </c>
+      <c r="P204" s="3" t="inlineStr">
+        <is>
+          <t>Agnuak</t>
+        </is>
+      </c>
       <c r="Q204" s="3" t="n"/>
       <c r="R204" s="3" t="n"/>
       <c r="S204" s="3" t="n"/>
@@ -18964,10 +19216,24 @@
           <t>HarariEthiopia</t>
         </is>
       </c>
-      <c r="M218" s="3" t="n"/>
-      <c r="N218" s="3" t="n"/>
-      <c r="O218" s="3" t="n"/>
-      <c r="P218" s="3" t="n"/>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O218" s="3" t="inlineStr">
+        <is>
+          <t>ET-HA</t>
+        </is>
+      </c>
+      <c r="P218" s="3" t="inlineStr">
+        <is>
+          <t>Hareri</t>
+        </is>
+      </c>
       <c r="Q218" s="3" t="n"/>
       <c r="R218" s="3" t="n"/>
       <c r="S218" s="3" t="n"/>
@@ -19068,10 +19334,22 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M219" s="3" t="n"/>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N219" s="3" t="n"/>
-      <c r="O219" s="3" t="n"/>
-      <c r="P219" s="3" t="n"/>
+      <c r="O219" s="3" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P219" s="3" t="inlineStr">
+        <is>
+          <t>አዳማ</t>
+        </is>
+      </c>
       <c r="Q219" s="3" t="n"/>
       <c r="R219" s="3" t="n"/>
       <c r="S219" s="3" t="n"/>
@@ -19170,10 +19448,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M220" s="3" t="n"/>
-      <c r="N220" s="3" t="n"/>
-      <c r="O220" s="3" t="n"/>
-      <c r="P220" s="3" t="n"/>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O220" s="3" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P220" s="3" t="inlineStr">
+        <is>
+          <t>East Shewa</t>
+        </is>
+      </c>
       <c r="Q220" s="3" t="n"/>
       <c r="R220" s="3" t="n"/>
       <c r="S220" s="3" t="n"/>
@@ -19272,10 +19564,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M221" s="2" t="n"/>
-      <c r="N221" s="2" t="n"/>
-      <c r="O221" s="2" t="n"/>
-      <c r="P221" s="2" t="n"/>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N221" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>West Shewa</t>
+        </is>
+      </c>
       <c r="Q221" s="2" t="n"/>
       <c r="R221" s="2" t="n"/>
       <c r="S221" s="2" t="n"/>
@@ -19362,10 +19668,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M222" s="2" t="n"/>
-      <c r="N222" s="2" t="n"/>
-      <c r="O222" s="2" t="n"/>
-      <c r="P222" s="2" t="n"/>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>West Shewa</t>
+        </is>
+      </c>
       <c r="Q222" s="2" t="n"/>
       <c r="R222" s="2" t="n"/>
       <c r="S222" s="2" t="n"/>
@@ -19452,10 +19772,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M223" s="2" t="n"/>
-      <c r="N223" s="2" t="n"/>
-      <c r="O223" s="2" t="n"/>
-      <c r="P223" s="2" t="n"/>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>West Shewa</t>
+        </is>
+      </c>
       <c r="Q223" s="2" t="n"/>
       <c r="R223" s="2" t="n"/>
       <c r="S223" s="2" t="n"/>
@@ -19542,10 +19876,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M224" s="2" t="n"/>
-      <c r="N224" s="2" t="n"/>
-      <c r="O224" s="2" t="n"/>
-      <c r="P224" s="2" t="n"/>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>South West Shewa</t>
+        </is>
+      </c>
       <c r="Q224" s="2" t="n"/>
       <c r="R224" s="2" t="n"/>
       <c r="S224" s="2" t="n"/>
@@ -19632,10 +19980,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M225" s="2" t="n"/>
-      <c r="N225" s="2" t="n"/>
-      <c r="O225" s="2" t="n"/>
-      <c r="P225" s="2" t="n"/>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>South West Shewa</t>
+        </is>
+      </c>
       <c r="Q225" s="2" t="n"/>
       <c r="R225" s="2" t="n"/>
       <c r="S225" s="2" t="n"/>
@@ -19722,10 +20084,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M226" s="2" t="n"/>
-      <c r="N226" s="2" t="n"/>
-      <c r="O226" s="2" t="n"/>
-      <c r="P226" s="2" t="n"/>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O226" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>South West Shewa</t>
+        </is>
+      </c>
       <c r="Q226" s="2" t="n"/>
       <c r="R226" s="2" t="n"/>
       <c r="S226" s="2" t="n"/>
@@ -19812,10 +20188,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M227" s="2" t="n"/>
-      <c r="N227" s="2" t="n"/>
-      <c r="O227" s="2" t="n"/>
-      <c r="P227" s="2" t="n"/>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>West Arsi</t>
+        </is>
+      </c>
       <c r="Q227" s="2" t="n"/>
       <c r="R227" s="2" t="n"/>
       <c r="S227" s="2" t="n"/>
@@ -19902,10 +20292,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M228" s="2" t="n"/>
-      <c r="N228" s="2" t="n"/>
-      <c r="O228" s="2" t="n"/>
-      <c r="P228" s="2" t="n"/>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O228" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>West Arsi</t>
+        </is>
+      </c>
       <c r="Q228" s="2" t="n"/>
       <c r="R228" s="2" t="n"/>
       <c r="S228" s="2" t="n"/>
@@ -19992,10 +20396,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M229" s="2" t="n"/>
-      <c r="N229" s="2" t="n"/>
-      <c r="O229" s="2" t="n"/>
-      <c r="P229" s="2" t="n"/>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>East Harerge</t>
+        </is>
+      </c>
       <c r="Q229" s="2" t="n"/>
       <c r="R229" s="2" t="n"/>
       <c r="S229" s="2" t="n"/>
@@ -20082,10 +20500,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M230" s="2" t="n"/>
-      <c r="N230" s="2" t="n"/>
-      <c r="O230" s="2" t="n"/>
-      <c r="P230" s="2" t="n"/>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>East Harerge</t>
+        </is>
+      </c>
       <c r="Q230" s="2" t="n"/>
       <c r="R230" s="2" t="n"/>
       <c r="S230" s="2" t="n"/>
@@ -20172,10 +20604,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M231" s="2" t="n"/>
-      <c r="N231" s="2" t="n"/>
-      <c r="O231" s="2" t="n"/>
-      <c r="P231" s="2" t="n"/>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>East Harerge</t>
+        </is>
+      </c>
       <c r="Q231" s="2" t="n"/>
       <c r="R231" s="2" t="n"/>
       <c r="S231" s="2" t="n"/>
@@ -20262,10 +20708,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M232" s="2" t="n"/>
-      <c r="N232" s="2" t="n"/>
-      <c r="O232" s="2" t="n"/>
-      <c r="P232" s="2" t="n"/>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>East Harerge</t>
+        </is>
+      </c>
       <c r="Q232" s="2" t="n"/>
       <c r="R232" s="2" t="n"/>
       <c r="S232" s="2" t="n"/>
@@ -20352,10 +20812,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M233" s="2" t="n"/>
-      <c r="N233" s="2" t="n"/>
-      <c r="O233" s="2" t="n"/>
-      <c r="P233" s="2" t="n"/>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>East Harerge</t>
+        </is>
+      </c>
       <c r="Q233" s="2" t="n"/>
       <c r="R233" s="2" t="n"/>
       <c r="S233" s="2" t="n"/>
@@ -20442,10 +20916,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M234" s="4" t="n"/>
-      <c r="N234" s="4" t="n"/>
-      <c r="O234" s="4" t="n"/>
-      <c r="P234" s="4" t="n"/>
+      <c r="M234" s="4" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N234" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O234" s="4" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P234" s="4" t="inlineStr">
+        <is>
+          <t>Jimma</t>
+        </is>
+      </c>
       <c r="Q234" s="4" t="n"/>
       <c r="R234" s="4" t="n"/>
       <c r="S234" s="4" t="n"/>
@@ -20546,10 +21034,24 @@
           <t>OromiaEthiopia</t>
         </is>
       </c>
-      <c r="M235" s="2" t="n"/>
-      <c r="N235" s="2" t="n"/>
-      <c r="O235" s="2" t="n"/>
-      <c r="P235" s="2" t="n"/>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N235" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>ET-OR</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>Jimma</t>
+        </is>
+      </c>
       <c r="Q235" s="2" t="n"/>
       <c r="R235" s="2" t="n"/>
       <c r="S235" s="2" t="n"/>
@@ -42868,10 +43370,24 @@
           <t>SidamaEthiopia</t>
         </is>
       </c>
-      <c r="M499" s="2" t="n"/>
-      <c r="N499" s="2" t="n"/>
-      <c r="O499" s="2" t="n"/>
-      <c r="P499" s="2" t="n"/>
+      <c r="M499" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N499" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O499" s="2" t="inlineStr">
+        <is>
+          <t>ET-SI</t>
+        </is>
+      </c>
+      <c r="P499" s="2" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
       <c r="Q499" s="2" t="n"/>
       <c r="R499" s="2" t="n"/>
       <c r="S499" s="2" t="n"/>
@@ -42958,10 +43474,24 @@
           <t>SidamaEthiopia</t>
         </is>
       </c>
-      <c r="M500" s="2" t="n"/>
-      <c r="N500" s="2" t="n"/>
-      <c r="O500" s="2" t="n"/>
-      <c r="P500" s="2" t="n"/>
+      <c r="M500" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N500" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O500" s="2" t="inlineStr">
+        <is>
+          <t>ET-SI</t>
+        </is>
+      </c>
+      <c r="P500" s="2" t="inlineStr">
+        <is>
+          <t>Sidama</t>
+        </is>
+      </c>
       <c r="Q500" s="2" t="n"/>
       <c r="R500" s="2" t="n"/>
       <c r="S500" s="2" t="n"/>
@@ -44560,10 +45090,24 @@
           <t>SomaliEthiopia</t>
         </is>
       </c>
-      <c r="M519" s="2" t="n"/>
-      <c r="N519" s="2" t="n"/>
-      <c r="O519" s="2" t="n"/>
-      <c r="P519" s="2" t="n"/>
+      <c r="M519" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N519" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O519" s="2" t="inlineStr">
+        <is>
+          <t>ET-SO</t>
+        </is>
+      </c>
+      <c r="P519" s="2" t="inlineStr">
+        <is>
+          <t>Fafan</t>
+        </is>
+      </c>
       <c r="Q519" s="2" t="n"/>
       <c r="R519" s="2" t="n"/>
       <c r="S519" s="2" t="n"/>
@@ -44650,10 +45194,24 @@
           <t>SomaliEthiopia</t>
         </is>
       </c>
-      <c r="M520" s="2" t="n"/>
-      <c r="N520" s="2" t="n"/>
-      <c r="O520" s="2" t="n"/>
-      <c r="P520" s="2" t="n"/>
+      <c r="M520" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N520" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O520" s="2" t="inlineStr">
+        <is>
+          <t>ET-SO</t>
+        </is>
+      </c>
+      <c r="P520" s="2" t="inlineStr">
+        <is>
+          <t>Fafan</t>
+        </is>
+      </c>
       <c r="Q520" s="2" t="n"/>
       <c r="R520" s="2" t="n"/>
       <c r="S520" s="2" t="n"/>
@@ -49064,10 +49622,24 @@
           <t>South WestEthiopia</t>
         </is>
       </c>
-      <c r="M572" s="2" t="n"/>
-      <c r="N572" s="2" t="n"/>
-      <c r="O572" s="2" t="n"/>
-      <c r="P572" s="2" t="n"/>
+      <c r="M572" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N572" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O572" s="2" t="inlineStr">
+        <is>
+          <t>ET-SW</t>
+        </is>
+      </c>
+      <c r="P572" s="2" t="inlineStr">
+        <is>
+          <t>Keffa</t>
+        </is>
+      </c>
       <c r="Q572" s="2" t="n"/>
       <c r="R572" s="2" t="n"/>
       <c r="S572" s="2" t="n"/>
@@ -49136,10 +49708,24 @@
           <t>South WestEthiopia</t>
         </is>
       </c>
-      <c r="M573" s="2" t="n"/>
-      <c r="N573" s="2" t="n"/>
-      <c r="O573" s="2" t="n"/>
-      <c r="P573" s="2" t="n"/>
+      <c r="M573" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N573" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O573" s="2" t="inlineStr">
+        <is>
+          <t>ET-SW</t>
+        </is>
+      </c>
+      <c r="P573" s="2" t="inlineStr">
+        <is>
+          <t>Keffa</t>
+        </is>
+      </c>
       <c r="Q573" s="2" t="n"/>
       <c r="R573" s="2" t="n"/>
       <c r="S573" s="2" t="n"/>
@@ -51154,10 +51740,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M603" s="2" t="n"/>
-      <c r="N603" s="2" t="n"/>
+      <c r="M603" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N603" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O603" s="2" t="n"/>
-      <c r="P603" s="2" t="n"/>
+      <c r="P603" s="2" t="inlineStr">
+        <is>
+          <t>Gamo Gofa</t>
+        </is>
+      </c>
       <c r="Q603" s="2" t="n"/>
       <c r="R603" s="2" t="n"/>
       <c r="S603" s="2" t="n"/>
@@ -51226,10 +51822,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M604" s="2" t="n"/>
-      <c r="N604" s="2" t="n"/>
+      <c r="M604" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N604" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O604" s="2" t="n"/>
-      <c r="P604" s="2" t="n"/>
+      <c r="P604" s="2" t="inlineStr">
+        <is>
+          <t>Hadiya</t>
+        </is>
+      </c>
       <c r="Q604" s="2" t="n"/>
       <c r="R604" s="2" t="n"/>
       <c r="S604" s="2" t="n"/>
@@ -51298,10 +51904,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M605" s="2" t="n"/>
-      <c r="N605" s="2" t="n"/>
+      <c r="M605" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N605" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O605" s="2" t="n"/>
-      <c r="P605" s="2" t="n"/>
+      <c r="P605" s="2" t="inlineStr">
+        <is>
+          <t>Hadiya</t>
+        </is>
+      </c>
       <c r="Q605" s="2" t="n"/>
       <c r="R605" s="2" t="n"/>
       <c r="S605" s="2" t="n"/>
@@ -51370,10 +51986,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M606" s="2" t="n"/>
-      <c r="N606" s="2" t="n"/>
+      <c r="M606" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N606" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O606" s="2" t="n"/>
-      <c r="P606" s="2" t="n"/>
+      <c r="P606" s="2" t="inlineStr">
+        <is>
+          <t>Wolayita</t>
+        </is>
+      </c>
       <c r="Q606" s="2" t="n"/>
       <c r="R606" s="2" t="n"/>
       <c r="S606" s="2" t="n"/>
@@ -51442,10 +52068,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M607" s="2" t="n"/>
-      <c r="N607" s="2" t="n"/>
+      <c r="M607" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N607" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O607" s="2" t="n"/>
-      <c r="P607" s="2" t="n"/>
+      <c r="P607" s="2" t="inlineStr">
+        <is>
+          <t>Wolayita</t>
+        </is>
+      </c>
       <c r="Q607" s="2" t="n"/>
       <c r="R607" s="2" t="n"/>
       <c r="S607" s="2" t="n"/>
@@ -51514,10 +52150,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M608" s="2" t="n"/>
-      <c r="N608" s="2" t="n"/>
+      <c r="M608" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N608" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O608" s="2" t="n"/>
-      <c r="P608" s="2" t="n"/>
+      <c r="P608" s="2" t="inlineStr">
+        <is>
+          <t>Gurage</t>
+        </is>
+      </c>
       <c r="Q608" s="2" t="n"/>
       <c r="R608" s="2" t="n"/>
       <c r="S608" s="2" t="n"/>
@@ -51586,10 +52232,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M609" s="2" t="n"/>
-      <c r="N609" s="2" t="n"/>
+      <c r="M609" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N609" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O609" s="2" t="n"/>
-      <c r="P609" s="2" t="n"/>
+      <c r="P609" s="2" t="inlineStr">
+        <is>
+          <t>Gurage</t>
+        </is>
+      </c>
       <c r="Q609" s="2" t="n"/>
       <c r="R609" s="2" t="n"/>
       <c r="S609" s="2" t="n"/>
@@ -51658,10 +52314,20 @@
           <t>Southern (SNNPR)Ethiopia</t>
         </is>
       </c>
-      <c r="M610" s="2" t="n"/>
-      <c r="N610" s="2" t="n"/>
+      <c r="M610" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N610" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="O610" s="2" t="n"/>
-      <c r="P610" s="2" t="n"/>
+      <c r="P610" s="2" t="inlineStr">
+        <is>
+          <t>Gurage</t>
+        </is>
+      </c>
       <c r="Q610" s="2" t="n"/>
       <c r="R610" s="2" t="n"/>
       <c r="S610" s="2" t="n"/>
@@ -57616,10 +58282,24 @@
           <t>TigrayEthiopia</t>
         </is>
       </c>
-      <c r="M699" s="2" t="n"/>
-      <c r="N699" s="2" t="n"/>
-      <c r="O699" s="2" t="n"/>
-      <c r="P699" s="2" t="n"/>
+      <c r="M699" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O699" s="2" t="inlineStr">
+        <is>
+          <t>ET-TI</t>
+        </is>
+      </c>
+      <c r="P699" s="2" t="inlineStr">
+        <is>
+          <t>Eastern</t>
+        </is>
+      </c>
       <c r="Q699" s="2" t="n"/>
       <c r="R699" s="2" t="n"/>
       <c r="S699" s="2" t="n"/>
@@ -57706,10 +58386,24 @@
           <t>TigrayEthiopia</t>
         </is>
       </c>
-      <c r="M700" s="2" t="n"/>
-      <c r="N700" s="2" t="n"/>
-      <c r="O700" s="2" t="n"/>
-      <c r="P700" s="2" t="n"/>
+      <c r="M700" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O700" s="2" t="inlineStr">
+        <is>
+          <t>ET-TI</t>
+        </is>
+      </c>
+      <c r="P700" s="2" t="inlineStr">
+        <is>
+          <t>Eastern</t>
+        </is>
+      </c>
       <c r="Q700" s="2" t="n"/>
       <c r="R700" s="2" t="n"/>
       <c r="S700" s="2" t="n"/>
@@ -57796,10 +58490,24 @@
           <t>TigrayEthiopia</t>
         </is>
       </c>
-      <c r="M701" s="2" t="n"/>
-      <c r="N701" s="2" t="n"/>
-      <c r="O701" s="2" t="n"/>
-      <c r="P701" s="2" t="n"/>
+      <c r="M701" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O701" s="2" t="inlineStr">
+        <is>
+          <t>ET-TI</t>
+        </is>
+      </c>
+      <c r="P701" s="2" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
       <c r="Q701" s="2" t="n"/>
       <c r="R701" s="2" t="n"/>
       <c r="S701" s="2" t="n"/>
@@ -57886,10 +58594,24 @@
           <t>TigrayEthiopia</t>
         </is>
       </c>
-      <c r="M702" s="2" t="n"/>
-      <c r="N702" s="2" t="n"/>
-      <c r="O702" s="2" t="n"/>
-      <c r="P702" s="2" t="n"/>
+      <c r="M702" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O702" s="2" t="inlineStr">
+        <is>
+          <t>ET-TI</t>
+        </is>
+      </c>
+      <c r="P702" s="2" t="inlineStr">
+        <is>
+          <t>Southern</t>
+        </is>
+      </c>
       <c r="Q702" s="2" t="n"/>
       <c r="R702" s="2" t="n"/>
       <c r="S702" s="2" t="n"/>
